--- a/excel/Windows快捷键总表.xlsx
+++ b/excel/Windows快捷键总表.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75FC57F3-FF4D-42E7-9495-DDDF7057A118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="343">
   <si>
     <t>快捷键组合</t>
   </si>
@@ -1048,13 +1049,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1081,15 +1088,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3CE2DDF-474A-4E25-B3A4-BA324C079CE9}" name="表1" displayName="表1" ref="A1:D118" totalsRowShown="0">
+  <autoFilter ref="A1:D118" xr:uid="{A3CE2DDF-474A-4E25-B3A4-BA324C079CE9}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{52CF5BBB-0E33-4EBE-8065-8D08D45F508F}" name="快捷键组合"/>
+    <tableColumn id="2" xr3:uid="{428C37FB-58BC-47BF-9656-B2ADC42485CF}" name="功能描述"/>
+    <tableColumn id="3" xr3:uid="{8E8B80F8-9726-429A-B66F-62C43EF4498F}" name="适用场景"/>
+    <tableColumn id="4" xr3:uid="{3CE1A881-1B4A-4A89-8588-8DFCE4F00367}" name="所属分类"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1345,17 +1378,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D118"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="31"/>
-    <col customWidth="true" max="2" min="2" width="30"/>
-    <col customWidth="true" max="3" min="3" width="12"/>
-    <col customWidth="true" max="4" min="4" width="48"/>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="44.6640625" customWidth="1"/>
+    <col min="3" max="3" width="71.53125" customWidth="1"/>
+    <col min="4" max="4" width="15.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1363,13 +1396,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
+    </row>
+    <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1383,7 +1416,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1391,13 +1424,13 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1405,13 +1438,13 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1419,13 +1452,13 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1433,13 +1466,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1447,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -1461,13 +1494,13 @@
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1475,13 +1508,13 @@
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -1489,13 +1522,13 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -1503,13 +1536,13 @@
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -1517,13 +1550,13 @@
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -1531,13 +1564,13 @@
         <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1545,13 +1578,13 @@
         <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -1559,13 +1592,13 @@
         <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -1573,13 +1606,13 @@
         <v>47</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -1587,13 +1620,13 @@
         <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>52</v>
       </c>
@@ -1601,13 +1634,13 @@
         <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>55</v>
       </c>
@@ -1615,13 +1648,13 @@
         <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>58</v>
       </c>
@@ -1629,13 +1662,13 @@
         <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>61</v>
       </c>
@@ -1643,13 +1676,13 @@
         <v>62</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>64</v>
       </c>
@@ -1657,13 +1690,13 @@
         <v>65</v>
       </c>
       <c r="C22" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="D22" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>67</v>
       </c>
@@ -1671,13 +1704,13 @@
         <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="D23" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>70</v>
       </c>
@@ -1685,13 +1718,13 @@
         <v>71</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="D24" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>73</v>
       </c>
@@ -1699,13 +1732,13 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>76</v>
       </c>
@@ -1713,13 +1746,13 @@
         <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>79</v>
       </c>
@@ -1727,13 +1760,13 @@
         <v>80</v>
       </c>
       <c r="C27" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>82</v>
       </c>
@@ -1741,13 +1774,13 @@
         <v>83</v>
       </c>
       <c r="C28" t="s">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="D28" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>85</v>
       </c>
@@ -1755,13 +1788,13 @@
         <v>86</v>
       </c>
       <c r="C29" t="s">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="D29" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>88</v>
       </c>
@@ -1769,13 +1802,13 @@
         <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="D30" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>91</v>
       </c>
@@ -1783,13 +1816,13 @@
         <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="D31" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>94</v>
       </c>
@@ -1797,13 +1830,13 @@
         <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>97</v>
       </c>
@@ -1811,13 +1844,13 @@
         <v>98</v>
       </c>
       <c r="C33" t="s">
+        <v>100</v>
+      </c>
+      <c r="D33" t="s">
         <v>99</v>
       </c>
-      <c r="D33" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34">
+    </row>
+    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>101</v>
       </c>
@@ -1825,13 +1858,13 @@
         <v>102</v>
       </c>
       <c r="C34" t="s">
+        <v>103</v>
+      </c>
+      <c r="D34" t="s">
         <v>99</v>
       </c>
-      <c r="D34" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="35">
+    </row>
+    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>104</v>
       </c>
@@ -1839,13 +1872,13 @@
         <v>105</v>
       </c>
       <c r="C35" t="s">
-        <v>8</v>
+        <v>106</v>
       </c>
       <c r="D35" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>107</v>
       </c>
@@ -1853,13 +1886,13 @@
         <v>108</v>
       </c>
       <c r="C36" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="D36" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>110</v>
       </c>
@@ -1867,13 +1900,13 @@
         <v>111</v>
       </c>
       <c r="C37" t="s">
-        <v>8</v>
+        <v>112</v>
       </c>
       <c r="D37" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>113</v>
       </c>
@@ -1881,13 +1914,13 @@
         <v>114</v>
       </c>
       <c r="C38" t="s">
-        <v>8</v>
+        <v>115</v>
       </c>
       <c r="D38" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>116</v>
       </c>
@@ -1895,13 +1928,13 @@
         <v>117</v>
       </c>
       <c r="C39" t="s">
+        <v>118</v>
+      </c>
+      <c r="D39" t="s">
         <v>99</v>
       </c>
-      <c r="D39" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="40">
+    </row>
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>119</v>
       </c>
@@ -1909,13 +1942,13 @@
         <v>120</v>
       </c>
       <c r="C40" t="s">
+        <v>121</v>
+      </c>
+      <c r="D40" t="s">
         <v>99</v>
       </c>
-      <c r="D40" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="41">
+    </row>
+    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>122</v>
       </c>
@@ -1929,7 +1962,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -1937,13 +1970,13 @@
         <v>124</v>
       </c>
       <c r="C42" t="s">
+        <v>126</v>
+      </c>
+      <c r="D42" t="s">
         <v>125</v>
       </c>
-      <c r="D42" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="43">
+    </row>
+    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>127</v>
       </c>
@@ -1951,13 +1984,13 @@
         <v>128</v>
       </c>
       <c r="C43" t="s">
+        <v>129</v>
+      </c>
+      <c r="D43" t="s">
         <v>125</v>
       </c>
-      <c r="D43" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="44">
+    </row>
+    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>130</v>
       </c>
@@ -1965,13 +1998,13 @@
         <v>131</v>
       </c>
       <c r="C44" t="s">
+        <v>132</v>
+      </c>
+      <c r="D44" t="s">
         <v>125</v>
       </c>
-      <c r="D44" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="45">
+    </row>
+    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>133</v>
       </c>
@@ -1979,13 +2012,13 @@
         <v>134</v>
       </c>
       <c r="C45" t="s">
+        <v>135</v>
+      </c>
+      <c r="D45" t="s">
         <v>125</v>
       </c>
-      <c r="D45" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="46">
+    </row>
+    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>136</v>
       </c>
@@ -1993,13 +2026,13 @@
         <v>137</v>
       </c>
       <c r="C46" t="s">
+        <v>138</v>
+      </c>
+      <c r="D46" t="s">
         <v>125</v>
       </c>
-      <c r="D46" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="47">
+    </row>
+    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>139</v>
       </c>
@@ -2013,7 +2046,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>140</v>
       </c>
@@ -2021,13 +2054,13 @@
         <v>141</v>
       </c>
       <c r="C48" t="s">
+        <v>143</v>
+      </c>
+      <c r="D48" t="s">
         <v>142</v>
       </c>
-      <c r="D48" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="49">
+    </row>
+    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>144</v>
       </c>
@@ -2035,13 +2068,13 @@
         <v>145</v>
       </c>
       <c r="C49" t="s">
+        <v>146</v>
+      </c>
+      <c r="D49" t="s">
         <v>142</v>
       </c>
-      <c r="D49" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="50">
+    </row>
+    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>147</v>
       </c>
@@ -2049,13 +2082,13 @@
         <v>148</v>
       </c>
       <c r="C50" t="s">
+        <v>149</v>
+      </c>
+      <c r="D50" t="s">
         <v>142</v>
       </c>
-      <c r="D50" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="51">
+    </row>
+    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>150</v>
       </c>
@@ -2063,13 +2096,13 @@
         <v>151</v>
       </c>
       <c r="C51" t="s">
+        <v>152</v>
+      </c>
+      <c r="D51" t="s">
         <v>142</v>
       </c>
-      <c r="D51" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="52">
+    </row>
+    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>153</v>
       </c>
@@ -2077,13 +2110,13 @@
         <v>154</v>
       </c>
       <c r="C52" t="s">
+        <v>155</v>
+      </c>
+      <c r="D52" t="s">
         <v>142</v>
       </c>
-      <c r="D52" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="53">
+    </row>
+    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>156</v>
       </c>
@@ -2091,13 +2124,13 @@
         <v>157</v>
       </c>
       <c r="C53" t="s">
+        <v>158</v>
+      </c>
+      <c r="D53" t="s">
         <v>142</v>
       </c>
-      <c r="D53" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="54">
+    </row>
+    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>159</v>
       </c>
@@ -2105,13 +2138,13 @@
         <v>160</v>
       </c>
       <c r="C54" t="s">
+        <v>161</v>
+      </c>
+      <c r="D54" t="s">
         <v>142</v>
       </c>
-      <c r="D54" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="55">
+    </row>
+    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>162</v>
       </c>
@@ -2119,13 +2152,13 @@
         <v>163</v>
       </c>
       <c r="C55" t="s">
+        <v>164</v>
+      </c>
+      <c r="D55" t="s">
         <v>142</v>
       </c>
-      <c r="D55" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="56">
+    </row>
+    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>165</v>
       </c>
@@ -2133,13 +2166,13 @@
         <v>166</v>
       </c>
       <c r="C56" t="s">
+        <v>167</v>
+      </c>
+      <c r="D56" t="s">
         <v>142</v>
       </c>
-      <c r="D56" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="57">
+    </row>
+    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>168</v>
       </c>
@@ -2147,13 +2180,13 @@
         <v>169</v>
       </c>
       <c r="C57" t="s">
+        <v>170</v>
+      </c>
+      <c r="D57" t="s">
         <v>142</v>
       </c>
-      <c r="D57" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="58">
+    </row>
+    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>171</v>
       </c>
@@ -2161,13 +2194,13 @@
         <v>172</v>
       </c>
       <c r="C58" t="s">
+        <v>173</v>
+      </c>
+      <c r="D58" t="s">
         <v>142</v>
       </c>
-      <c r="D58" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="59">
+    </row>
+    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>174</v>
       </c>
@@ -2175,13 +2208,13 @@
         <v>175</v>
       </c>
       <c r="C59" t="s">
+        <v>176</v>
+      </c>
+      <c r="D59" t="s">
         <v>142</v>
       </c>
-      <c r="D59" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="60">
+    </row>
+    <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>177</v>
       </c>
@@ -2189,13 +2222,13 @@
         <v>178</v>
       </c>
       <c r="C60" t="s">
+        <v>179</v>
+      </c>
+      <c r="D60" t="s">
         <v>142</v>
       </c>
-      <c r="D60" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="61">
+    </row>
+    <row r="61" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>180</v>
       </c>
@@ -2203,13 +2236,13 @@
         <v>181</v>
       </c>
       <c r="C61" t="s">
+        <v>182</v>
+      </c>
+      <c r="D61" t="s">
         <v>142</v>
       </c>
-      <c r="D61" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="62">
+    </row>
+    <row r="62" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>183</v>
       </c>
@@ -2217,13 +2250,13 @@
         <v>184</v>
       </c>
       <c r="C62" t="s">
+        <v>185</v>
+      </c>
+      <c r="D62" t="s">
         <v>142</v>
       </c>
-      <c r="D62" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="63">
+    </row>
+    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>186</v>
       </c>
@@ -2231,13 +2264,13 @@
         <v>187</v>
       </c>
       <c r="C63" t="s">
+        <v>188</v>
+      </c>
+      <c r="D63" t="s">
         <v>142</v>
       </c>
-      <c r="D63" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="64">
+    </row>
+    <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>189</v>
       </c>
@@ -2251,7 +2284,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>190</v>
       </c>
@@ -2259,13 +2292,13 @@
         <v>191</v>
       </c>
       <c r="C65" t="s">
+        <v>193</v>
+      </c>
+      <c r="D65" t="s">
         <v>192</v>
       </c>
-      <c r="D65" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="66">
+    </row>
+    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>194</v>
       </c>
@@ -2273,13 +2306,13 @@
         <v>195</v>
       </c>
       <c r="C66" t="s">
+        <v>196</v>
+      </c>
+      <c r="D66" t="s">
         <v>192</v>
       </c>
-      <c r="D66" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="67">
+    </row>
+    <row r="67" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>197</v>
       </c>
@@ -2287,13 +2320,13 @@
         <v>198</v>
       </c>
       <c r="C67" t="s">
+        <v>199</v>
+      </c>
+      <c r="D67" t="s">
         <v>192</v>
       </c>
-      <c r="D67" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="68">
+    </row>
+    <row r="68" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>200</v>
       </c>
@@ -2301,13 +2334,13 @@
         <v>201</v>
       </c>
       <c r="C68" t="s">
+        <v>202</v>
+      </c>
+      <c r="D68" t="s">
         <v>192</v>
       </c>
-      <c r="D68" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="69">
+    </row>
+    <row r="69" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>203</v>
       </c>
@@ -2315,13 +2348,13 @@
         <v>204</v>
       </c>
       <c r="C69" t="s">
+        <v>206</v>
+      </c>
+      <c r="D69" t="s">
         <v>205</v>
       </c>
-      <c r="D69" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="70">
+    </row>
+    <row r="70" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>207</v>
       </c>
@@ -2329,13 +2362,13 @@
         <v>208</v>
       </c>
       <c r="C70" t="s">
+        <v>209</v>
+      </c>
+      <c r="D70" t="s">
         <v>205</v>
       </c>
-      <c r="D70" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="71">
+    </row>
+    <row r="71" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>210</v>
       </c>
@@ -2349,7 +2382,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>211</v>
       </c>
@@ -2357,13 +2390,13 @@
         <v>212</v>
       </c>
       <c r="C72" t="s">
+        <v>214</v>
+      </c>
+      <c r="D72" t="s">
         <v>213</v>
       </c>
-      <c r="D72" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="73">
+    </row>
+    <row r="73" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>215</v>
       </c>
@@ -2371,13 +2404,13 @@
         <v>216</v>
       </c>
       <c r="C73" t="s">
+        <v>217</v>
+      </c>
+      <c r="D73" t="s">
         <v>213</v>
       </c>
-      <c r="D73" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="74">
+    </row>
+    <row r="74" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>218</v>
       </c>
@@ -2385,13 +2418,13 @@
         <v>219</v>
       </c>
       <c r="C74" t="s">
+        <v>220</v>
+      </c>
+      <c r="D74" t="s">
         <v>213</v>
       </c>
-      <c r="D74" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="75">
+    </row>
+    <row r="75" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>221</v>
       </c>
@@ -2399,13 +2432,13 @@
         <v>222</v>
       </c>
       <c r="C75" t="s">
+        <v>224</v>
+      </c>
+      <c r="D75" t="s">
         <v>223</v>
       </c>
-      <c r="D75" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="76">
+    </row>
+    <row r="76" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>225</v>
       </c>
@@ -2419,7 +2452,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>226</v>
       </c>
@@ -2427,13 +2460,13 @@
         <v>227</v>
       </c>
       <c r="C77" t="s">
+        <v>229</v>
+      </c>
+      <c r="D77" t="s">
         <v>228</v>
       </c>
-      <c r="D77" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="78">
+    </row>
+    <row r="78" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>230</v>
       </c>
@@ -2441,13 +2474,13 @@
         <v>231</v>
       </c>
       <c r="C78" t="s">
+        <v>232</v>
+      </c>
+      <c r="D78" t="s">
         <v>228</v>
       </c>
-      <c r="D78" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="79">
+    </row>
+    <row r="79" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>233</v>
       </c>
@@ -2455,13 +2488,13 @@
         <v>234</v>
       </c>
       <c r="C79" t="s">
+        <v>235</v>
+      </c>
+      <c r="D79" t="s">
         <v>228</v>
       </c>
-      <c r="D79" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="80">
+    </row>
+    <row r="80" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>236</v>
       </c>
@@ -2475,7 +2508,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>237</v>
       </c>
@@ -2483,13 +2516,13 @@
         <v>238</v>
       </c>
       <c r="C81" t="s">
+        <v>240</v>
+      </c>
+      <c r="D81" t="s">
         <v>239</v>
       </c>
-      <c r="D81" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="82">
+    </row>
+    <row r="82" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>241</v>
       </c>
@@ -2497,13 +2530,13 @@
         <v>242</v>
       </c>
       <c r="C82" t="s">
+        <v>243</v>
+      </c>
+      <c r="D82" t="s">
         <v>239</v>
       </c>
-      <c r="D82" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="83">
+    </row>
+    <row r="83" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>244</v>
       </c>
@@ -2511,13 +2544,13 @@
         <v>245</v>
       </c>
       <c r="C83" t="s">
+        <v>246</v>
+      </c>
+      <c r="D83" t="s">
         <v>239</v>
       </c>
-      <c r="D83" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="84">
+    </row>
+    <row r="84" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>247</v>
       </c>
@@ -2525,13 +2558,13 @@
         <v>248</v>
       </c>
       <c r="C84" t="s">
+        <v>249</v>
+      </c>
+      <c r="D84" t="s">
         <v>239</v>
       </c>
-      <c r="D84" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="85">
+    </row>
+    <row r="85" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>250</v>
       </c>
@@ -2539,13 +2572,13 @@
         <v>251</v>
       </c>
       <c r="C85" t="s">
+        <v>252</v>
+      </c>
+      <c r="D85" t="s">
         <v>239</v>
       </c>
-      <c r="D85" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="86">
+    </row>
+    <row r="86" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>253</v>
       </c>
@@ -2553,13 +2586,13 @@
         <v>254</v>
       </c>
       <c r="C86" t="s">
+        <v>255</v>
+      </c>
+      <c r="D86" t="s">
         <v>239</v>
       </c>
-      <c r="D86" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="87">
+    </row>
+    <row r="87" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>256</v>
       </c>
@@ -2567,13 +2600,13 @@
         <v>257</v>
       </c>
       <c r="C87" t="s">
+        <v>258</v>
+      </c>
+      <c r="D87" t="s">
         <v>239</v>
       </c>
-      <c r="D87" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="88">
+    </row>
+    <row r="88" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>259</v>
       </c>
@@ -2581,13 +2614,13 @@
         <v>260</v>
       </c>
       <c r="C88" t="s">
+        <v>261</v>
+      </c>
+      <c r="D88" t="s">
         <v>239</v>
       </c>
-      <c r="D88" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="89">
+    </row>
+    <row r="89" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>262</v>
       </c>
@@ -2595,13 +2628,13 @@
         <v>263</v>
       </c>
       <c r="C89" t="s">
+        <v>264</v>
+      </c>
+      <c r="D89" t="s">
         <v>239</v>
       </c>
-      <c r="D89" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="90">
+    </row>
+    <row r="90" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>265</v>
       </c>
@@ -2609,13 +2642,13 @@
         <v>266</v>
       </c>
       <c r="C90" t="s">
+        <v>267</v>
+      </c>
+      <c r="D90" t="s">
         <v>239</v>
       </c>
-      <c r="D90" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="91">
+    </row>
+    <row r="91" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>268</v>
       </c>
@@ -2629,7 +2662,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>269</v>
       </c>
@@ -2637,13 +2670,13 @@
         <v>270</v>
       </c>
       <c r="C92" t="s">
+        <v>271</v>
+      </c>
+      <c r="D92" t="s">
         <v>99</v>
       </c>
-      <c r="D92" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="93">
+    </row>
+    <row r="93" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>272</v>
       </c>
@@ -2651,13 +2684,13 @@
         <v>273</v>
       </c>
       <c r="C93" t="s">
+        <v>274</v>
+      </c>
+      <c r="D93" t="s">
         <v>99</v>
       </c>
-      <c r="D93" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="94">
+    </row>
+    <row r="94" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>275</v>
       </c>
@@ -2665,13 +2698,13 @@
         <v>276</v>
       </c>
       <c r="C94" t="s">
+        <v>277</v>
+      </c>
+      <c r="D94" t="s">
         <v>99</v>
       </c>
-      <c r="D94" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="95">
+    </row>
+    <row r="95" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>278</v>
       </c>
@@ -2679,13 +2712,13 @@
         <v>279</v>
       </c>
       <c r="C95" t="s">
+        <v>280</v>
+      </c>
+      <c r="D95" t="s">
         <v>99</v>
       </c>
-      <c r="D95" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="96">
+    </row>
+    <row r="96" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>281</v>
       </c>
@@ -2693,13 +2726,13 @@
         <v>282</v>
       </c>
       <c r="C96" t="s">
+        <v>283</v>
+      </c>
+      <c r="D96" t="s">
         <v>99</v>
       </c>
-      <c r="D96" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="97">
+    </row>
+    <row r="97" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>284</v>
       </c>
@@ -2713,7 +2746,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>285</v>
       </c>
@@ -2721,13 +2754,13 @@
         <v>286</v>
       </c>
       <c r="C98" t="s">
+        <v>288</v>
+      </c>
+      <c r="D98" t="s">
         <v>287</v>
       </c>
-      <c r="D98" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="99">
+    </row>
+    <row r="99" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>147</v>
       </c>
@@ -2735,13 +2768,13 @@
         <v>289</v>
       </c>
       <c r="C99" t="s">
+        <v>290</v>
+      </c>
+      <c r="D99" t="s">
         <v>287</v>
       </c>
-      <c r="D99" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="100">
+    </row>
+    <row r="100" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>291</v>
       </c>
@@ -2749,13 +2782,13 @@
         <v>292</v>
       </c>
       <c r="C100" t="s">
+        <v>293</v>
+      </c>
+      <c r="D100" t="s">
         <v>287</v>
       </c>
-      <c r="D100" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="101">
+    </row>
+    <row r="101" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>294</v>
       </c>
@@ -2763,13 +2796,13 @@
         <v>295</v>
       </c>
       <c r="C101" t="s">
+        <v>296</v>
+      </c>
+      <c r="D101" t="s">
         <v>287</v>
       </c>
-      <c r="D101" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="102">
+    </row>
+    <row r="102" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>297</v>
       </c>
@@ -2777,13 +2810,13 @@
         <v>298</v>
       </c>
       <c r="C102" t="s">
+        <v>299</v>
+      </c>
+      <c r="D102" t="s">
         <v>287</v>
       </c>
-      <c r="D102" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="103">
+    </row>
+    <row r="103" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>300</v>
       </c>
@@ -2791,13 +2824,13 @@
         <v>301</v>
       </c>
       <c r="C103" t="s">
+        <v>302</v>
+      </c>
+      <c r="D103" t="s">
         <v>287</v>
       </c>
-      <c r="D103" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="104">
+    </row>
+    <row r="104" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>303</v>
       </c>
@@ -2805,13 +2838,13 @@
         <v>304</v>
       </c>
       <c r="C104" t="s">
+        <v>305</v>
+      </c>
+      <c r="D104" t="s">
         <v>287</v>
       </c>
-      <c r="D104" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="105">
+    </row>
+    <row r="105" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>306</v>
       </c>
@@ -2819,13 +2852,13 @@
         <v>307</v>
       </c>
       <c r="C105" t="s">
+        <v>308</v>
+      </c>
+      <c r="D105" t="s">
         <v>287</v>
       </c>
-      <c r="D105" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="106">
+    </row>
+    <row r="106" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>309</v>
       </c>
@@ -2839,7 +2872,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>310</v>
       </c>
@@ -2847,13 +2880,13 @@
         <v>311</v>
       </c>
       <c r="C107" t="s">
+        <v>313</v>
+      </c>
+      <c r="D107" t="s">
         <v>312</v>
       </c>
-      <c r="D107" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="108">
+    </row>
+    <row r="108" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>314</v>
       </c>
@@ -2861,13 +2894,13 @@
         <v>315</v>
       </c>
       <c r="C108" t="s">
+        <v>316</v>
+      </c>
+      <c r="D108" t="s">
         <v>312</v>
       </c>
-      <c r="D108" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="109">
+    </row>
+    <row r="109" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>317</v>
       </c>
@@ -2875,13 +2908,13 @@
         <v>318</v>
       </c>
       <c r="C109" t="s">
+        <v>319</v>
+      </c>
+      <c r="D109" t="s">
         <v>312</v>
       </c>
-      <c r="D109" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="110">
+    </row>
+    <row r="110" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>244</v>
       </c>
@@ -2889,13 +2922,13 @@
         <v>320</v>
       </c>
       <c r="C110" t="s">
+        <v>321</v>
+      </c>
+      <c r="D110" t="s">
         <v>312</v>
       </c>
-      <c r="D110" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="111">
+    </row>
+    <row r="111" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>322</v>
       </c>
@@ -2903,13 +2936,13 @@
         <v>323</v>
       </c>
       <c r="C111" t="s">
+        <v>324</v>
+      </c>
+      <c r="D111" t="s">
         <v>312</v>
       </c>
-      <c r="D111" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="112">
+    </row>
+    <row r="112" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>325</v>
       </c>
@@ -2923,7 +2956,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>140</v>
       </c>
@@ -2931,13 +2964,13 @@
         <v>326</v>
       </c>
       <c r="C113" t="s">
+        <v>327</v>
+      </c>
+      <c r="D113" t="s">
         <v>312</v>
       </c>
-      <c r="D113" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="114">
+    </row>
+    <row r="114" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>328</v>
       </c>
@@ -2945,13 +2978,13 @@
         <v>329</v>
       </c>
       <c r="C114" t="s">
+        <v>330</v>
+      </c>
+      <c r="D114" t="s">
         <v>312</v>
       </c>
-      <c r="D114" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="115">
+    </row>
+    <row r="115" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>331</v>
       </c>
@@ -2959,13 +2992,13 @@
         <v>332</v>
       </c>
       <c r="C115" t="s">
+        <v>333</v>
+      </c>
+      <c r="D115" t="s">
         <v>312</v>
       </c>
-      <c r="D115" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="116">
+    </row>
+    <row r="116" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>334</v>
       </c>
@@ -2973,13 +3006,13 @@
         <v>335</v>
       </c>
       <c r="C116" t="s">
+        <v>336</v>
+      </c>
+      <c r="D116" t="s">
         <v>312</v>
       </c>
-      <c r="D116" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="117">
+    </row>
+    <row r="117" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>337</v>
       </c>
@@ -2987,13 +3020,13 @@
         <v>338</v>
       </c>
       <c r="C117" t="s">
+        <v>339</v>
+      </c>
+      <c r="D117" t="s">
         <v>312</v>
       </c>
-      <c r="D117" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="118">
+    </row>
+    <row r="118" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>340</v>
       </c>
@@ -3001,12 +3034,17 @@
         <v>341</v>
       </c>
       <c r="C118" t="s">
+        <v>342</v>
+      </c>
+      <c r="D118" t="s">
         <v>312</v>
       </c>
-      <c r="D118" t="s">
-        <v>342</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>